--- a/log/update_list.xlsx
+++ b/log/update_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v5.4_20260122\log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v5.5_20260403\log\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9ABC6F4-CAB8-4930-A875-45DA3EFB767A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C067C2A9-B537-42B9-8478-263C0AAC6246}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -694,6 +694,41 @@
 c.支持新增自定义关键字，同MP标签页规则，关键字信息在compare_information.xlsx表Sheet3中，不是关键字的信息内容会被归纳为'Unkown'，可自行修改原excel表格中信息；
 d.'Unkown'选择不支持条件筛选，其余均支持条件组合筛选；
 e.空字符、’/‘字符均被归纳为NULL项，可支持条件筛选；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP List Check Tool_v5.5_20260403</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新list：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.Check标签页:
+a.Check页面增加整机ITO信息检查：对比整机最新ITO的MP bin版本与模组端的最新版本是否一致；
+b.屏蔽check all时候的序号校正功能；
+c.补充新IC、玻璃信息；
+2.Analyse/MP标签页：
+a.新增整机ITO筛选项：ALL、Y、N，类似于flash，且支持其他关联项筛选；</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1172,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.375" customWidth="1"/>
@@ -1302,6 +1337,14 @@
       </c>
       <c r="B15" s="6" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="99.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/log/update_list.xlsx
+++ b/log/update_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\TOOL python project\MP TOOL PROJECT_v5.5_20260403\log\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Desktop\MP TOOL\MP_List_Check_Tool_v5.7_20260703\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C067C2A9-B537-42B9-8478-263C0AAC6246}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{702DDA0C-DD5F-46F8-A508-DA0923440919}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>版本号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -730,6 +730,50 @@
 2.Analyse/MP标签页：
 a.新增整机ITO筛选项：ALL、Y、N，类似于flash，且支持其他关联项筛选；</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP List Check Tool_v5.6_20260702</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>更新list：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.Analyse/MP标签页：
+  a.新增半年度选项(下拉框内容位于年度下方)：All、上半年、下半年，与年度选项一起组合，支持半年度的数据分析；
+    i.当”年度“下拉框内容不为ALL时，”半年度“支持任意组合数据分析；
+    ii.项目统计”年度“和”半年度“支持互相筛选数据分析。
+  b.补充新IC、玻璃信息；</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MP List Check Tool_v5.7_20260703</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新list：
+1.Analyse/客诉分析：
+  a..新增半年度选项(下拉框内容位于年度下方)：All、上半年、下半年，与年度选项一起组合，支持半年度的数据分析，功能与规则同MP分析界面；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1207,7 +1251,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.375" customWidth="1"/>
@@ -1345,6 +1389,22 @@
       </c>
       <c r="B16" s="6" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="85.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
